--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T05:34:40+00:00</t>
+    <t>2026-09-17T07:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:46:21+00:00</t>
+    <t>2026-09-17T12:50:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:50:52+00:00</t>
+    <t>2026-09-18T07:26:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +88,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet mit Codes für Substanzen und Stoffe, die als Auslöser von Allergien oder Intoleranzen erfasst werden.</t>
+    <t>Value-Set für die Codierung von Allergien und Intoleranzen.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,6 +101,12 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>ValueSet URL</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-wirkstoffe-ages</t>
   </si>
   <si>
     <t>Operation</t>
@@ -389,6 +396,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -401,7 +432,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -409,13 +440,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -428,10 +459,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:26:42+00:00</t>
+    <t>2026-09-29T15:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="504">
   <si>
     <t>Property</t>
   </si>
@@ -49,7 +49,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:00:21+00:00</t>
+    <t>2026-09-30T11:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -109,16 +109,1417 @@
     <t>https://termgit.elga.gv.at/ValueSet/elga-wirkstoffe-ages</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>concept</t>
-  </si>
-  <si>
-    <t>is-a</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>432003</t>
+  </si>
+  <si>
+    <t>2159007</t>
+  </si>
+  <si>
+    <t>2309006</t>
+  </si>
+  <si>
+    <t>2799001</t>
+  </si>
+  <si>
+    <t>3692009</t>
+  </si>
+  <si>
+    <t>3718001</t>
+  </si>
+  <si>
+    <t>3829006</t>
+  </si>
+  <si>
+    <t>6725000</t>
+  </si>
+  <si>
+    <t>7434003</t>
+  </si>
+  <si>
+    <t>7791007</t>
+  </si>
+  <si>
+    <t>8204009</t>
+  </si>
+  <si>
+    <t>9010006</t>
+  </si>
+  <si>
+    <t>9021002</t>
+  </si>
+  <si>
+    <t>10827009</t>
+  </si>
+  <si>
+    <t>11526002</t>
+  </si>
+  <si>
+    <t>12503006</t>
+  </si>
+  <si>
+    <t>12510000</t>
+  </si>
+  <si>
+    <t>13577000</t>
+  </si>
+  <si>
+    <t>13652007</t>
+  </si>
+  <si>
+    <t>14006006</t>
+  </si>
+  <si>
+    <t>14321009</t>
+  </si>
+  <si>
+    <t>14402002</t>
+  </si>
+  <si>
+    <t>15896008</t>
+  </si>
+  <si>
+    <t>16313001</t>
+  </si>
+  <si>
+    <t>17172002</t>
+  </si>
+  <si>
+    <t>17486007</t>
+  </si>
+  <si>
+    <t>17693003</t>
+  </si>
+  <si>
+    <t>19839007</t>
+  </si>
+  <si>
+    <t>19893005</t>
+  </si>
+  <si>
+    <t>21592006</t>
+  </si>
+  <si>
+    <t>22242006</t>
+  </si>
+  <si>
+    <t>22836000</t>
+  </si>
+  <si>
+    <t>22931006</t>
+  </si>
+  <si>
+    <t>22968009</t>
+  </si>
+  <si>
+    <t>23182003</t>
+  </si>
+  <si>
+    <t>24102007</t>
+  </si>
+  <si>
+    <t>24215009</t>
+  </si>
+  <si>
+    <t>25761002</t>
+  </si>
+  <si>
+    <t>27119002</t>
+  </si>
+  <si>
+    <t>28230009</t>
+  </si>
+  <si>
+    <t>28421003</t>
+  </si>
+  <si>
+    <t>28647000</t>
+  </si>
+  <si>
+    <t>29263009</t>
+  </si>
+  <si>
+    <t>29522004</t>
+  </si>
+  <si>
+    <t>31006001</t>
+  </si>
+  <si>
+    <t>31347007</t>
+  </si>
+  <si>
+    <t>33008008</t>
+  </si>
+  <si>
+    <t>33396006</t>
+  </si>
+  <si>
+    <t>35233000</t>
+  </si>
+  <si>
+    <t>35605007</t>
+  </si>
+  <si>
+    <t>35609001</t>
+  </si>
+  <si>
+    <t>37017009</t>
+  </si>
+  <si>
+    <t>37575004</t>
+  </si>
+  <si>
+    <t>38271009</t>
+  </si>
+  <si>
+    <t>41750006</t>
+  </si>
+  <si>
+    <t>41967008</t>
+  </si>
+  <si>
+    <t>42416001</t>
+  </si>
+  <si>
+    <t>43230003</t>
+  </si>
+  <si>
+    <t>43735007</t>
+  </si>
+  <si>
+    <t>44027008</t>
+  </si>
+  <si>
+    <t>47703008</t>
+  </si>
+  <si>
+    <t>48540004</t>
+  </si>
+  <si>
+    <t>50593009</t>
+  </si>
+  <si>
+    <t>51503008</t>
+  </si>
+  <si>
+    <t>51905005</t>
+  </si>
+  <si>
+    <t>51963001</t>
+  </si>
+  <si>
+    <t>52454007</t>
+  </si>
+  <si>
+    <t>52836003</t>
+  </si>
+  <si>
+    <t>54041009</t>
+  </si>
+  <si>
+    <t>55700001</t>
+  </si>
+  <si>
+    <t>56822005</t>
+  </si>
+  <si>
+    <t>57126000</t>
+  </si>
+  <si>
+    <t>57720001</t>
+  </si>
+  <si>
+    <t>59351004</t>
+  </si>
+  <si>
+    <t>59533004</t>
+  </si>
+  <si>
+    <t>59545008</t>
+  </si>
+  <si>
+    <t>61088005</t>
+  </si>
+  <si>
+    <t>61789006</t>
+  </si>
+  <si>
+    <t>63338004</t>
+  </si>
+  <si>
+    <t>63766005</t>
+  </si>
+  <si>
+    <t>64601002</t>
+  </si>
+  <si>
+    <t>65123005</t>
+  </si>
+  <si>
+    <t>65345002</t>
+  </si>
+  <si>
+    <t>66562002</t>
+  </si>
+  <si>
+    <t>66925006</t>
+  </si>
+  <si>
+    <t>67324005</t>
+  </si>
+  <si>
+    <t>68524009</t>
+  </si>
+  <si>
+    <t>71463006</t>
+  </si>
+  <si>
+    <t>72179002</t>
+  </si>
+  <si>
+    <t>72511004</t>
+  </si>
+  <si>
+    <t>73892005</t>
+  </si>
+  <si>
+    <t>75044009</t>
+  </si>
+  <si>
+    <t>75665004</t>
+  </si>
+  <si>
+    <t>77249007</t>
+  </si>
+  <si>
+    <t>79549001</t>
+  </si>
+  <si>
+    <t>80237000</t>
+  </si>
+  <si>
+    <t>81911001</t>
+  </si>
+  <si>
+    <t>82566005</t>
+  </si>
+  <si>
+    <t>83595008</t>
+  </si>
+  <si>
+    <t>83619009</t>
+  </si>
+  <si>
+    <t>84181009</t>
+  </si>
+  <si>
+    <t>84212004</t>
+  </si>
+  <si>
+    <t>84791008</t>
+  </si>
+  <si>
+    <t>85066006</t>
+  </si>
+  <si>
+    <t>89811004</t>
+  </si>
+  <si>
+    <t>89889006</t>
+  </si>
+  <si>
+    <t>102259006</t>
+  </si>
+  <si>
+    <t>102261002</t>
+  </si>
+  <si>
+    <t>102262009</t>
+  </si>
+  <si>
+    <t>102263004</t>
+  </si>
+  <si>
+    <t>102264005</t>
+  </si>
+  <si>
+    <t>102697003</t>
   </si>
   <si>
     <t>105590001</t>
+  </si>
+  <si>
+    <t>111088007</t>
+  </si>
+  <si>
+    <t>111095003</t>
+  </si>
+  <si>
+    <t>115589000</t>
+  </si>
+  <si>
+    <t>116364004</t>
+  </si>
+  <si>
+    <t>116549003</t>
+  </si>
+  <si>
+    <t>116637007</t>
+  </si>
+  <si>
+    <t>119417004</t>
+  </si>
+  <si>
+    <t>125706008</t>
+  </si>
+  <si>
+    <t>128488006</t>
+  </si>
+  <si>
+    <t>128489003</t>
+  </si>
+  <si>
+    <t>226491003</t>
+  </si>
+  <si>
+    <t>226723006</t>
+  </si>
+  <si>
+    <t>226776001</t>
+  </si>
+  <si>
+    <t>226791004</t>
+  </si>
+  <si>
+    <t>226793001</t>
+  </si>
+  <si>
+    <t>226915003</t>
+  </si>
+  <si>
+    <t>226916002</t>
+  </si>
+  <si>
+    <t>226934003</t>
+  </si>
+  <si>
+    <t>226942002</t>
+  </si>
+  <si>
+    <t>226955001</t>
+  </si>
+  <si>
+    <t>226963000</t>
+  </si>
+  <si>
+    <t>226967004</t>
+  </si>
+  <si>
+    <t>227042005</t>
+  </si>
+  <si>
+    <t>227066004</t>
+  </si>
+  <si>
+    <t>227067008</t>
+  </si>
+  <si>
+    <t>227072004</t>
+  </si>
+  <si>
+    <t>227078000</t>
+  </si>
+  <si>
+    <t>227081005</t>
+  </si>
+  <si>
+    <t>227083008</t>
+  </si>
+  <si>
+    <t>227099002</t>
+  </si>
+  <si>
+    <t>227105000</t>
+  </si>
+  <si>
+    <t>227106004</t>
+  </si>
+  <si>
+    <t>227131003</t>
+  </si>
+  <si>
+    <t>227136008</t>
+  </si>
+  <si>
+    <t>227139001</t>
+  </si>
+  <si>
+    <t>227144008</t>
+  </si>
+  <si>
+    <t>227147001</t>
+  </si>
+  <si>
+    <t>227150003</t>
+  </si>
+  <si>
+    <t>227151004</t>
+  </si>
+  <si>
+    <t>227156009</t>
+  </si>
+  <si>
+    <t>227183005</t>
+  </si>
+  <si>
+    <t>227215000</t>
+  </si>
+  <si>
+    <t>227219006</t>
+  </si>
+  <si>
+    <t>227220000</t>
+  </si>
+  <si>
+    <t>227227002</t>
+  </si>
+  <si>
+    <t>227229004</t>
+  </si>
+  <si>
+    <t>227230009</t>
+  </si>
+  <si>
+    <t>227313005</t>
+  </si>
+  <si>
+    <t>227339008</t>
+  </si>
+  <si>
+    <t>227346004</t>
+  </si>
+  <si>
+    <t>227350006</t>
+  </si>
+  <si>
+    <t>227362005</t>
+  </si>
+  <si>
+    <t>227374009</t>
+  </si>
+  <si>
+    <t>227376006</t>
+  </si>
+  <si>
+    <t>227379004</t>
+  </si>
+  <si>
+    <t>227382009</t>
+  </si>
+  <si>
+    <t>227383004</t>
+  </si>
+  <si>
+    <t>227385006</t>
+  </si>
+  <si>
+    <t>227387003</t>
+  </si>
+  <si>
+    <t>227388008</t>
+  </si>
+  <si>
+    <t>227389000</t>
+  </si>
+  <si>
+    <t>227390009</t>
+  </si>
+  <si>
+    <t>227391008</t>
+  </si>
+  <si>
+    <t>227392001</t>
+  </si>
+  <si>
+    <t>227395004</t>
+  </si>
+  <si>
+    <t>227396003</t>
+  </si>
+  <si>
+    <t>227398002</t>
+  </si>
+  <si>
+    <t>227400003</t>
+  </si>
+  <si>
+    <t>227404007</t>
+  </si>
+  <si>
+    <t>227405008</t>
+  </si>
+  <si>
+    <t>227407000</t>
+  </si>
+  <si>
+    <t>227408005</t>
+  </si>
+  <si>
+    <t>227409002</t>
+  </si>
+  <si>
+    <t>227410007</t>
+  </si>
+  <si>
+    <t>227411006</t>
+  </si>
+  <si>
+    <t>227413009</t>
+  </si>
+  <si>
+    <t>227414003</t>
+  </si>
+  <si>
+    <t>227423000</t>
+  </si>
+  <si>
+    <t>227425007</t>
+  </si>
+  <si>
+    <t>227435001</t>
+  </si>
+  <si>
+    <t>227444000</t>
+  </si>
+  <si>
+    <t>227447007</t>
+  </si>
+  <si>
+    <t>227493005</t>
+  </si>
+  <si>
+    <t>227501001</t>
+  </si>
+  <si>
+    <t>227511008</t>
+  </si>
+  <si>
+    <t>227512001</t>
+  </si>
+  <si>
+    <t>227514000</t>
+  </si>
+  <si>
+    <t>227515004</t>
+  </si>
+  <si>
+    <t>227538001</t>
+  </si>
+  <si>
+    <t>227598003</t>
+  </si>
+  <si>
+    <t>228104004</t>
+  </si>
+  <si>
+    <t>229934002</t>
+  </si>
+  <si>
+    <t>229941008</t>
+  </si>
+  <si>
+    <t>229944000</t>
+  </si>
+  <si>
+    <t>230034002</t>
+  </si>
+  <si>
+    <t>255620007</t>
+  </si>
+  <si>
+    <t>255640000</t>
+  </si>
+  <si>
+    <t>255667006</t>
+  </si>
+  <si>
+    <t>255764006</t>
+  </si>
+  <si>
+    <t>255769001</t>
+  </si>
+  <si>
+    <t>255772008</t>
+  </si>
+  <si>
+    <t>255775005</t>
+  </si>
+  <si>
+    <t>255786007</t>
+  </si>
+  <si>
+    <t>255814009</t>
+  </si>
+  <si>
+    <t>255840003</t>
+  </si>
+  <si>
+    <t>255842006</t>
+  </si>
+  <si>
+    <t>255844007</t>
+  </si>
+  <si>
+    <t>255859001</t>
+  </si>
+  <si>
+    <t>255864002</t>
+  </si>
+  <si>
+    <t>255868004</t>
+  </si>
+  <si>
+    <t>255871007</t>
+  </si>
+  <si>
+    <t>255924000</t>
+  </si>
+  <si>
+    <t>256186006</t>
+  </si>
+  <si>
+    <t>256218005</t>
+  </si>
+  <si>
+    <t>256259004</t>
+  </si>
+  <si>
+    <t>256260009</t>
+  </si>
+  <si>
+    <t>256262001</t>
+  </si>
+  <si>
+    <t>256267007</t>
+  </si>
+  <si>
+    <t>256270006</t>
+  </si>
+  <si>
+    <t>256272003</t>
+  </si>
+  <si>
+    <t>256277009</t>
+  </si>
+  <si>
+    <t>256281009</t>
+  </si>
+  <si>
+    <t>256289006</t>
+  </si>
+  <si>
+    <t>256290002</t>
+  </si>
+  <si>
+    <t>256292005</t>
+  </si>
+  <si>
+    <t>256293000</t>
+  </si>
+  <si>
+    <t>256303006</t>
+  </si>
+  <si>
+    <t>256305004</t>
+  </si>
+  <si>
+    <t>256306003</t>
+  </si>
+  <si>
+    <t>256307007</t>
+  </si>
+  <si>
+    <t>256313003</t>
+  </si>
+  <si>
+    <t>256315005</t>
+  </si>
+  <si>
+    <t>256316006</t>
+  </si>
+  <si>
+    <t>256317002</t>
+  </si>
+  <si>
+    <t>256318007</t>
+  </si>
+  <si>
+    <t>256319004</t>
+  </si>
+  <si>
+    <t>256326004</t>
+  </si>
+  <si>
+    <t>256329006</t>
+  </si>
+  <si>
+    <t>256330001</t>
+  </si>
+  <si>
+    <t>256331002</t>
+  </si>
+  <si>
+    <t>256350002</t>
+  </si>
+  <si>
+    <t>256351003</t>
+  </si>
+  <si>
+    <t>256352005</t>
+  </si>
+  <si>
+    <t>256353000</t>
+  </si>
+  <si>
+    <t>256354006</t>
+  </si>
+  <si>
+    <t>256355007</t>
+  </si>
+  <si>
+    <t>256363008</t>
+  </si>
+  <si>
+    <t>256417003</t>
+  </si>
+  <si>
+    <t>256419000</t>
+  </si>
+  <si>
+    <t>256435007</t>
+  </si>
+  <si>
+    <t>256440004</t>
+  </si>
+  <si>
+    <t>256443002</t>
+  </si>
+  <si>
+    <t>256496006</t>
+  </si>
+  <si>
+    <t>256501007</t>
+  </si>
+  <si>
+    <t>256504004</t>
+  </si>
+  <si>
+    <t>256506002</t>
+  </si>
+  <si>
+    <t>256526003</t>
+  </si>
+  <si>
+    <t>256579008</t>
+  </si>
+  <si>
+    <t>256596009</t>
+  </si>
+  <si>
+    <t>256607001</t>
+  </si>
+  <si>
+    <t>256633009</t>
+  </si>
+  <si>
+    <t>259221006</t>
+  </si>
+  <si>
+    <t>260108001</t>
+  </si>
+  <si>
+    <t>260118006</t>
+  </si>
+  <si>
+    <t>260126003</t>
+  </si>
+  <si>
+    <t>260131001</t>
+  </si>
+  <si>
+    <t>260152009</t>
+  </si>
+  <si>
+    <t>260153004</t>
+  </si>
+  <si>
+    <t>260154005</t>
+  </si>
+  <si>
+    <t>260156007</t>
+  </si>
+  <si>
+    <t>260167008</t>
+  </si>
+  <si>
+    <t>260168003</t>
+  </si>
+  <si>
+    <t>260176001</t>
+  </si>
+  <si>
+    <t>260177005</t>
+  </si>
+  <si>
+    <t>260179008</t>
+  </si>
+  <si>
+    <t>260184002</t>
+  </si>
+  <si>
+    <t>260189007</t>
+  </si>
+  <si>
+    <t>260204008</t>
+  </si>
+  <si>
+    <t>260205009</t>
+  </si>
+  <si>
+    <t>261243003</t>
+  </si>
+  <si>
+    <t>261249004</t>
+  </si>
+  <si>
+    <t>261250004</t>
+  </si>
+  <si>
+    <t>261712009</t>
+  </si>
+  <si>
+    <t>264287008</t>
+  </si>
+  <si>
+    <t>264295007</t>
+  </si>
+  <si>
+    <t>264331002</t>
+  </si>
+  <si>
+    <t>264337003</t>
+  </si>
+  <si>
+    <t>276310004</t>
+  </si>
+  <si>
+    <t>277016007</t>
+  </si>
+  <si>
+    <t>278840001</t>
+  </si>
+  <si>
+    <t>280939008</t>
+  </si>
+  <si>
+    <t>286550009</t>
+  </si>
+  <si>
+    <t>288326000</t>
+  </si>
+  <si>
+    <t>288328004</t>
+  </si>
+  <si>
+    <t>288460008</t>
+  </si>
+  <si>
+    <t>289122001</t>
+  </si>
+  <si>
+    <t>289949002</t>
+  </si>
+  <si>
+    <t>289955007</t>
+  </si>
+  <si>
+    <t>290008007</t>
+  </si>
+  <si>
+    <t>301093003</t>
+  </si>
+  <si>
+    <t>301712000</t>
+  </si>
+  <si>
+    <t>303300008</t>
+  </si>
+  <si>
+    <t>303314008</t>
+  </si>
+  <si>
+    <t>303315009</t>
+  </si>
+  <si>
+    <t>311443003</t>
+  </si>
+  <si>
+    <t>311731000</t>
+  </si>
+  <si>
+    <t>311846002</t>
+  </si>
+  <si>
+    <t>373780001</t>
+  </si>
+  <si>
+    <t>387239001</t>
+  </si>
+  <si>
+    <t>387293003</t>
+  </si>
+  <si>
+    <t>391737006</t>
+  </si>
+  <si>
+    <t>395734009</t>
+  </si>
+  <si>
+    <t>396049000</t>
+  </si>
+  <si>
+    <t>398705004</t>
+  </si>
+  <si>
+    <t>408742009</t>
+  </si>
+  <si>
+    <t>409595003</t>
+  </si>
+  <si>
+    <t>410853002</t>
+  </si>
+  <si>
+    <t>412056003</t>
+  </si>
+  <si>
+    <t>412060000</t>
+  </si>
+  <si>
+    <t>412061001</t>
+  </si>
+  <si>
+    <t>412068007</t>
+  </si>
+  <si>
+    <t>412070003</t>
+  </si>
+  <si>
+    <t>412071004</t>
+  </si>
+  <si>
+    <t>412145001</t>
+  </si>
+  <si>
+    <t>412150007</t>
+  </si>
+  <si>
+    <t>412153009</t>
+  </si>
+  <si>
+    <t>412156001</t>
+  </si>
+  <si>
+    <t>412161004</t>
+  </si>
+  <si>
+    <t>412357001</t>
+  </si>
+  <si>
+    <t>412548006</t>
+  </si>
+  <si>
+    <t>415710007</t>
+  </si>
+  <si>
+    <t>418266005</t>
+  </si>
+  <si>
+    <t>418504009</t>
+  </si>
+  <si>
+    <t>418785009</t>
+  </si>
+  <si>
+    <t>418920007</t>
+  </si>
+  <si>
+    <t>419420009</t>
+  </si>
+  <si>
+    <t>419604006</t>
+  </si>
+  <si>
+    <t>419633007</t>
+  </si>
+  <si>
+    <t>421556008</t>
+  </si>
+  <si>
+    <t>425620007</t>
+  </si>
+  <si>
+    <t>430503006</t>
+  </si>
+  <si>
+    <t>431510009</t>
+  </si>
+  <si>
+    <t>434162003</t>
+  </si>
+  <si>
+    <t>472731004</t>
+  </si>
+  <si>
+    <t>698730007</t>
+  </si>
+  <si>
+    <t>702730004</t>
+  </si>
+  <si>
+    <t>710039005</t>
+  </si>
+  <si>
+    <t>710171001</t>
+  </si>
+  <si>
+    <t>710172008</t>
+  </si>
+  <si>
+    <t>710178007</t>
+  </si>
+  <si>
+    <t>710179004</t>
+  </si>
+  <si>
+    <t>710183004</t>
+  </si>
+  <si>
+    <t>710184005</t>
+  </si>
+  <si>
+    <t>710226003</t>
+  </si>
+  <si>
+    <t>710900003</t>
+  </si>
+  <si>
+    <t>710902006</t>
+  </si>
+  <si>
+    <t>710930006</t>
+  </si>
+  <si>
+    <t>710932003</t>
+  </si>
+  <si>
+    <t>710937009</t>
+  </si>
+  <si>
+    <t>710943006</t>
+  </si>
+  <si>
+    <t>711088004</t>
+  </si>
+  <si>
+    <t>711089007</t>
+  </si>
+  <si>
+    <t>711090003</t>
+  </si>
+  <si>
+    <t>711092006</t>
+  </si>
+  <si>
+    <t>711094007</t>
+  </si>
+  <si>
+    <t>711096009</t>
+  </si>
+  <si>
+    <t>711097000</t>
+  </si>
+  <si>
+    <t>711098005</t>
+  </si>
+  <si>
+    <t>711143002</t>
+  </si>
+  <si>
+    <t>711316002</t>
+  </si>
+  <si>
+    <t>711319009</t>
+  </si>
+  <si>
+    <t>719108000</t>
+  </si>
+  <si>
+    <t>720687003</t>
+  </si>
+  <si>
+    <t>726731009</t>
+  </si>
+  <si>
+    <t>726749009</t>
+  </si>
+  <si>
+    <t>726755004</t>
+  </si>
+  <si>
+    <t>726758002</t>
+  </si>
+  <si>
+    <t>726759005</t>
+  </si>
+  <si>
+    <t>726761001</t>
+  </si>
+  <si>
+    <t>726763003</t>
+  </si>
+  <si>
+    <t>726764009</t>
+  </si>
+  <si>
+    <t>734881000</t>
+  </si>
+  <si>
+    <t>735004000</t>
+  </si>
+  <si>
+    <t>735006003</t>
+  </si>
+  <si>
+    <t>735009005</t>
+  </si>
+  <si>
+    <t>735029006</t>
+  </si>
+  <si>
+    <t>735030001</t>
+  </si>
+  <si>
+    <t>735034005</t>
+  </si>
+  <si>
+    <t>735035006</t>
+  </si>
+  <si>
+    <t>735042006</t>
+  </si>
+  <si>
+    <t>735043001</t>
+  </si>
+  <si>
+    <t>735045008</t>
+  </si>
+  <si>
+    <t>735046009</t>
+  </si>
+  <si>
+    <t>735047000</t>
+  </si>
+  <si>
+    <t>735049002</t>
+  </si>
+  <si>
+    <t>735050002</t>
+  </si>
+  <si>
+    <t>735051003</t>
+  </si>
+  <si>
+    <t>735053000</t>
+  </si>
+  <si>
+    <t>735106000</t>
+  </si>
+  <si>
+    <t>735123009</t>
+  </si>
+  <si>
+    <t>735124003</t>
+  </si>
+  <si>
+    <t>735211005</t>
+  </si>
+  <si>
+    <t>735212003</t>
+  </si>
+  <si>
+    <t>735213008</t>
+  </si>
+  <si>
+    <t>735214002</t>
+  </si>
+  <si>
+    <t>735215001</t>
+  </si>
+  <si>
+    <t>735245003</t>
+  </si>
+  <si>
+    <t>735246002</t>
+  </si>
+  <si>
+    <t>735248001</t>
+  </si>
+  <si>
+    <t>735249009</t>
+  </si>
+  <si>
+    <t>735336002</t>
+  </si>
+  <si>
+    <t>735337006</t>
+  </si>
+  <si>
+    <t>735340006</t>
+  </si>
+  <si>
+    <t>735341005</t>
+  </si>
+  <si>
+    <t>735959004</t>
+  </si>
+  <si>
+    <t>735971005</t>
+  </si>
+  <si>
+    <t>735972003</t>
+  </si>
+  <si>
+    <t>735974002</t>
+  </si>
+  <si>
+    <t>735977009</t>
+  </si>
+  <si>
+    <t>735979007</t>
+  </si>
+  <si>
+    <t>736027000</t>
+  </si>
+  <si>
+    <t>736030007</t>
+  </si>
+  <si>
+    <t>736031006</t>
+  </si>
+  <si>
+    <t>736159005</t>
+  </si>
+  <si>
+    <t>736162008</t>
+  </si>
+  <si>
+    <t>736258006</t>
+  </si>
+  <si>
+    <t>762766007</t>
+  </si>
+  <si>
+    <t>762952008</t>
+  </si>
+  <si>
+    <t>764166003</t>
+  </si>
+  <si>
+    <t>765099008</t>
+  </si>
+  <si>
+    <t>767406000</t>
+  </si>
+  <si>
+    <t>770326002</t>
+  </si>
+  <si>
+    <t>771518004</t>
+  </si>
+  <si>
+    <t>772245002</t>
+  </si>
+  <si>
+    <t>773757000</t>
+  </si>
+  <si>
+    <t>782576004</t>
+  </si>
+  <si>
+    <t>785344003</t>
+  </si>
+  <si>
+    <t>1003736004</t>
+  </si>
+  <si>
+    <t>1003752001</t>
+  </si>
+  <si>
+    <t>1137358000</t>
+  </si>
+  <si>
+    <t>1137359008</t>
+  </si>
+  <si>
+    <t>442461000124102</t>
+  </si>
+  <si>
+    <t>24515005</t>
+  </si>
+  <si>
+    <t>37663002</t>
+  </si>
+  <si>
+    <t>51386004</t>
+  </si>
+  <si>
+    <t>63045006</t>
+  </si>
+  <si>
+    <t>70813002</t>
+  </si>
+  <si>
+    <t>80259003</t>
+  </si>
+  <si>
+    <t>87918000</t>
+  </si>
+  <si>
+    <t>116274004</t>
+  </si>
+  <si>
+    <t>227038007</t>
+  </si>
+  <si>
+    <t>227110001</t>
+  </si>
+  <si>
+    <t>256248008</t>
+  </si>
+  <si>
+    <t>256406004</t>
+  </si>
+  <si>
+    <t>289954006</t>
+  </si>
+  <si>
+    <t>735108004</t>
+  </si>
+  <si>
+    <t>442571000124108</t>
   </si>
   <si>
     <t>System URI</t>
@@ -420,7 +1821,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B473"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -429,40 +1830,2846 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>34</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
         <v>36</v>
+      </c>
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B64" s="2"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B66" s="2"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B67" s="2"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B68" s="2"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B69" s="2"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B70" s="2"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B71" s="2"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B72" s="2"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B73" s="2"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B74" s="2"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B75" s="2"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B76" s="2"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B77" s="2"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B78" s="2"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B79" s="2"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B80" s="2"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B81" s="2"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B82" s="2"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B83" s="2"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B84" s="2"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B85" s="2"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B86" s="2"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B87" s="2"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B88" s="2"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B89" s="2"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B90" s="2"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B91" s="2"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B92" s="2"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B93" s="2"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B94" s="2"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B95" s="2"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B96" s="2"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B97" s="2"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B98" s="2"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B99" s="2"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B100" s="2"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B101" s="2"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B102" s="2"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B103" s="2"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B104" s="2"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B105" s="2"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B106" s="2"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B107" s="2"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B108" s="2"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B109" s="2"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B110" s="2"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B111" s="2"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B112" s="2"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B113" s="2"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B114" s="2"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B115" s="2"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B116" s="2"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B117" s="2"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B118" s="2"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B119" s="2"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B120" s="2"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B121" s="2"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B122" s="2"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B123" s="2"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B124" s="2"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B125" s="2"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B126" s="2"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B127" s="2"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B128" s="2"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B129" s="2"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B130" s="2"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B131" s="2"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B132" s="2"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B133" s="2"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B134" s="2"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B135" s="2"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B136" s="2"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B137" s="2"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B138" s="2"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B139" s="2"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B140" s="2"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B141" s="2"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B142" s="2"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B143" s="2"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B144" s="2"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B145" s="2"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B146" s="2"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B147" s="2"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B148" s="2"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B149" s="2"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B157" s="2"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B158" s="2"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B159" s="2"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B160" s="2"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B161" s="2"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B162" s="2"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B163" s="2"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B164" s="2"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B165" s="2"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B166" s="2"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B167" s="2"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B168" s="2"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B169" s="2"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B170" s="2"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B171" s="2"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B172" s="2"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B173" s="2"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B174" s="2"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B175" s="2"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B176" s="2"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B177" s="2"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B178" s="2"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B179" s="2"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B180" s="2"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B181" s="2"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B182" s="2"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B183" s="2"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B184" s="2"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B185" s="2"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B186" s="2"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B187" s="2"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B188" s="2"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B189" s="2"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B190" s="2"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B191" s="2"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B192" s="2"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B193" s="2"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B194" s="2"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B195" s="2"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B196" s="2"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B197" s="2"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B198" s="2"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B199" s="2"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B200" s="2"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B201" s="2"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B202" s="2"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B203" s="2"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B204" s="2"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B205" s="2"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B206" s="2"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B207" s="2"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B208" s="2"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B209" s="2"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B210" s="2"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B211" s="2"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B212" s="2"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B213" s="2"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B214" s="2"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B215" s="2"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B216" s="2"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B217" s="2"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B218" s="2"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B219" s="2"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B220" s="2"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B221" s="2"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B222" s="2"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B223" s="2"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B224" s="2"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B225" s="2"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B226" s="2"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B227" s="2"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B228" s="2"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B229" s="2"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B230" s="2"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B231" s="2"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B232" s="2"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B233" s="2"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B234" s="2"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B235" s="2"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B236" s="2"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B237" s="2"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B238" s="2"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B239" s="2"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B240" s="2"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B241" s="2"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B242" s="2"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B243" s="2"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B244" s="2"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B245" s="2"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B246" s="2"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B247" s="2"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B248" s="2"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B249" s="2"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B250" s="2"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B251" s="2"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B252" s="2"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B253" s="2"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B254" s="2"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B255" s="2"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B256" s="2"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B257" s="2"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B258" s="2"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B259" s="2"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B260" s="2"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B261" s="2"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B262" s="2"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B263" s="2"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B264" s="2"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B265" s="2"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B266" s="2"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B267" s="2"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B268" s="2"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B269" s="2"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B270" s="2"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B271" s="2"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B272" s="2"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B273" s="2"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B274" s="2"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B275" s="2"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B276" s="2"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B277" s="2"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B278" s="2"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B279" s="2"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B280" s="2"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B281" s="2"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B282" s="2"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B283" s="2"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B284" s="2"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B285" s="2"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B286" s="2"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B287" s="2"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B288" s="2"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B289" s="2"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B290" s="2"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B291" s="2"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B292" s="2"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B293" s="2"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B294" s="2"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B295" s="2"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B296" s="2"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B297" s="2"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B298" s="2"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B299" s="2"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B300" s="2"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B301" s="2"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B302" s="2"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B303" s="2"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B304" s="2"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B305" s="2"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B306" s="2"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B307" s="2"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B308" s="2"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B309" s="2"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B310" s="2"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B311" s="2"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B312" s="2"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B313" s="2"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B314" s="2"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B315" s="2"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B316" s="2"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B317" s="2"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B318" s="2"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B319" s="2"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B320" s="2"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B321" s="2"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B322" s="2"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B323" s="2"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B324" s="2"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B325" s="2"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B326" s="2"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B327" s="2"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B328" s="2"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B329" s="2"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B330" s="2"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B331" s="2"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B332" s="2"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B333" s="2"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B334" s="2"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B335" s="2"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B336" s="2"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B337" s="2"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B338" s="2"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B339" s="2"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B340" s="2"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B341" s="2"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B342" s="2"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B343" s="2"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B344" s="2"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B345" s="2"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B346" s="2"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B347" s="2"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B348" s="2"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B349" s="2"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B350" s="2"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B351" s="2"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B352" s="2"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B353" s="2"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B354" s="2"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B355" s="2"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B356" s="2"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B357" s="2"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B358" s="2"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B359" s="2"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B360" s="2"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B361" s="2"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B362" s="2"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B363" s="2"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B364" s="2"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B365" s="2"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B366" s="2"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B367" s="2"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B368" s="2"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B369" s="2"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B370" s="2"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B371" s="2"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B372" s="2"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B373" s="2"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B374" s="2"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B375" s="2"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B376" s="2"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B377" s="2"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B378" s="2"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B379" s="2"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B380" s="2"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B381" s="2"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B382" s="2"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B383" s="2"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B384" s="2"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B385" s="2"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B386" s="2"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B387" s="2"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B388" s="2"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B389" s="2"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B390" s="2"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B391" s="2"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B392" s="2"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B393" s="2"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B394" s="2"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B395" s="2"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B396" s="2"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B397" s="2"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B398" s="2"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B399" s="2"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B400" s="2"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B401" s="2"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B402" s="2"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B403" s="2"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B404" s="2"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B405" s="2"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B406" s="2"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B407" s="2"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B408" s="2"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B409" s="2"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B410" s="2"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B411" s="2"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B412" s="2"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B413" s="2"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B414" s="2"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B415" s="2"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B416" s="2"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B417" s="2"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B418" s="2"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B419" s="2"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B420" s="2"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B421" s="2"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B422" s="2"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B423" s="2"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B424" s="2"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B425" s="2"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B426" s="2"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B427" s="2"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B428" s="2"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B429" s="2"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B430" s="2"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B431" s="2"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B432" s="2"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B433" s="2"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B434" s="2"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B435" s="2"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B436" s="2"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B437" s="2"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B438" s="2"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B439" s="2"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B440" s="2"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B441" s="2"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B442" s="2"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B443" s="2"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B444" s="2"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B445" s="2"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B446" s="2"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B447" s="2"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B448" s="2"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B449" s="2"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B450" s="2"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B451" s="2"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B452" s="2"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B453" s="2"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B454" s="2"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B455" s="2"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B456" s="2"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B457" s="2"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B458" s="2"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B459" s="2"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B460" s="2"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B461" s="2"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B462" s="2"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B463" s="2"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B464" s="2"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B465" s="2"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B466" s="2"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B467" s="2"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B468" s="2"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B469" s="2"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B470" s="2"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B471" s="2"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B472" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B473" t="s" s="2">
+        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:14:45+00:00</t>
+    <t>2026-09-30T12:38:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:38:12+00:00</t>
+    <t>2026-09-30T12:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:52:09+00:00</t>
+    <t>2026-09-30T14:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T14:46:14+00:00</t>
+    <t>2026-10-01T13:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:01:54+00:00</t>
+    <t>2026-10-02T12:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T12:58:24+00:00</t>
+    <t>2026-10-07T14:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T14:48:24+00:00</t>
+    <t>2026-10-08T12:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:55:57+00:00</t>
+    <t>2026-10-08T13:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T13:59:28+00:00</t>
+    <t>2026-10-08T14:12:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:12:43+00:00</t>
+    <t>2026-10-08T15:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T15:20:56+00:00</t>
+    <t>2026-10-09T06:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:09:27+00:00</t>
+    <t>2026-10-09T08:15:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:15:54+00:00</t>
+    <t>2026-10-09T08:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:42:14+00:00</t>
+    <t>2026-10-09T09:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:07:37+00:00</t>
+    <t>2026-10-09T12:41:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T12:41:54+00:00</t>
+    <t>2026-10-12T13:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:54:53+00:00</t>
+    <t>2026-10-12T14:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:06:36+00:00</t>
+    <t>2026-10-12T14:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:31:02+00:00</t>
+    <t>2026-10-13T07:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:15:40+00:00</t>
+    <t>2026-10-14T06:31:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T06:31:33+00:00</t>
+    <t>2026-10-15T07:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T07:03:41+00:00</t>
+    <t>2026-10-16T09:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
